--- a/examples/sample.xlsx
+++ b/examples/sample.xlsx
@@ -10,6 +10,7 @@
     <sheet name="売上" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Regions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Notes" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Formulas" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -899,4 +900,199 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>A2&amp;" x "&amp;B2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pear</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>B3&gt;C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>B2+B3</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>$C$2+1</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>D2+D3</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>(B2+C2)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>'売上'!C2</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>'売上'!E2</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>10%*C2</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>1/0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>B5*2</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>B6^2</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>-D2</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>"a"="A"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>func</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>SUM(B2:B3)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>1+"2"</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>B2=120</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cycle</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>E7</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8">
+        <f>E7</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/examples/sample.xlsx
+++ b/examples/sample.xlsx
@@ -908,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1092,6 +1092,29 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>func2</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>IF(B2&gt;100,"many","few")</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>ROUND(C5/7,2)</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>COUNTA(A2:A9)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>TEXT(D2,"#,##0")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
